--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,10 +503,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>19.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Szpala L.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Saputo Stadium
@@ -562,10 +567,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>19.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chapman A.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Bank of America Stadium
@@ -621,10 +631,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>19.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lauziere P.
+ (Can)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Audi Field
@@ -680,10 +695,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>19.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Boiko S.
+ (Ukr)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Chase Stadium
@@ -739,10 +759,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>19.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Penso C.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>BMO Field
@@ -798,10 +823,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19.06.2024 20:45</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>19.06.2024 23:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marrufo J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>TQL Stadium
@@ -857,10 +887,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>20.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Unkel T.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Q2 Stadium
@@ -916,10 +951,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>20.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Demianchuk S.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Toyota Stadium
@@ -975,10 +1015,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>20.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fischer D.
+ (Can)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Shell Energy Stadium
@@ -1034,10 +1079,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>20.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Allatin M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Children's Mercy Park
@@ -1093,10 +1143,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>20.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gonzales G.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>CITYPARK
@@ -1139,6 +1194,134 @@
         <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Vazquez R.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>167</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>De Oliveira M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PayPal Park
+ (San Jose, CA)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>167</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2024</t>
         </is>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,50 +498,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Szpala L.
+          <t>De Oliveira M.
  (Usa)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saputo Stadium
- (Montreal, QC)</t>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23 112</t>
+          <t>20 371</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -562,50 +562,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chapman A.
+          <t>Ford T.
  (Usa)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bank of America Stadium
- (Charlotte, NC)</t>
+          <t>Audi Field
+ (Washington, DC)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74 500</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -626,50 +626,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lauziere P.
- (Can)</t>
-        </is>
-      </c>
+          <t>22.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Audi Field
- (Washington, DC)</t>
+          <t>TQL Stadium
+ (Cincinnati, OH)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20 000</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -690,626 +685,626 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>Dickerson J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>167</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>22.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Simon N.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Inter&amp;Co Stadium
+ (Orlando, FL)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25 500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>167</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Da Silva A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Subaru Park
+ (Chester, PA)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>167</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fischer D.
+ (Can)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19 400</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>167</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rivas V.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Geodis Park
+ (Nashville, TN)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>167</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dujic F.
+ (Can)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>22 423</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>167</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22.06.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mendoza R.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>167</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22.06.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marrufo J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>167</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Boiko S.
  (Ukr)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Chase Stadium
- (Fort Lauderdale, FL)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>21 550</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BMO Stadium
+ (Los Angeles, CA)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>167</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L13" t="n">
         <v>1671</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WA7tw22b</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>19.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Penso C.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BMO Field
- (Toronto, ON)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30 991</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Toronto FC</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>167</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MTkoJCzn</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>19.06.2024 23:45</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Marrufo J.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TQL Stadium
- (Cincinnati, OH)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>26 000</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>FC Cincinnati</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>167</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>zg5jGAK4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>20.06.2024 00:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Unkel T.
  (Usa)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Q2 Stadium
- (Austin, TX)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>20 700</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Austin FC</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>167</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ld9fFUZA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>20.06.2024 00:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Demianchuk S.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Toyota Stadium
- (Frisco, TX)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20 500</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>167</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WKbaElkH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20.06.2024 00:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Fischer D.
- (Can)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Shell Energy Stadium
- (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>22 039</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>167</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ABc3D84N</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>20.06.2024 00:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Allatin M.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park
- (Kansas City, MO)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>18 500</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sporting Kansas City</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>167</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vo27CSJT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20.06.2024 00:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Gonzales G.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CITYPARK
- (St. Louis, MO)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>22 423</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>167</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tflZ7nSp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20.06.2024 02:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Vazquez R.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Dignity Health Sports Park
- (Carson, CA)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>27 000</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Los Angeles Galaxy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>167</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>raSHWV4o</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>20.06.2024 02:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>De Oliveira M.
- (Usa)</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PayPal Park
- (San Jose, CA)</t>
+          <t>Providence Park
+ (Portland, OR)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18 000</t>
+          <t>25 218</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1322,6 +1317,70 @@
         <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Badawi M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lumen Field
+ (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>72 000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>167</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2024</t>
         </is>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
+          <t>23.06.2024 00:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
+          <t>23.06.2024 00:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
+          <t>23.06.2024 00:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22.06.2024 22:30</t>
+          <t>23.06.2024 01:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22.06.2024 22:30</t>
+          <t>23.06.2024 01:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>23.06.2024 02:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>23.06.2024 02:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>23.06.2024 02:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1386,6 +1386,1599 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>28.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Yankee Stadium
+ (New York, NY)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>54 251</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>167</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>71 000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>167</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>23 112</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>167</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>68 756</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>167</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>167</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>167</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>22 039</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>167</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Geodis Park
+ (Nashville, TN)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>167</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>167</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BMO Stadium
+ (Los Angeles, CA)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>167</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Providence Park
+ (Portland, OR)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>25 218</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>167</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PayPal Park
+ (San Jose, CA)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>167</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lumen Field
+ (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>72 000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>167</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BC Place
+ (Vancouver, BC)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>54 405</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>167</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>03.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20 371</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>167</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bank of America Stadium
+ (Charlotte, NC)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>74 500</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>167</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Audi Field
+ (Washington, DC)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>167</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Yankee Stadium
+ (New York, NY)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>54 251</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>167</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BMO Field
+ (Toronto, ON)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>30 991</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>167</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:45</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>68 756</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>167</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>04.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Soldier Field
+ (Chicago, IL)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>61 500</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>167</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>04.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19 400</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>167</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>04.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>22 423</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>167</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>04.07.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>167</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>05.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>167</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>05.07.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>167</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>05.07.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>167</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
+          <t>22.06.2024 20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23.06.2024 00:30</t>
+          <t>22.06.2024 21:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23.06.2024 00:30</t>
+          <t>22.06.2024 21:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23.06.2024 00:30</t>
+          <t>22.06.2024 21:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23.06.2024 01:30</t>
+          <t>22.06.2024 22:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.06.2024 01:30</t>
+          <t>22.06.2024 22:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23.06.2024 02:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23.06.2024 02:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23.06.2024 02:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,20 +476,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -503,7 +523,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,16 +564,36 @@
           <t>Sporting Kansas City</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vermes peter</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>167</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>1671</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -567,7 +607,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,16 +648,36 @@
           <t>Houston Dynamo</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>lesesne troy</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>olsen ben</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>167</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>1671</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -631,10 +691,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Freemon J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>TQL Stadium
@@ -667,16 +732,36 @@
           <t>New England Revolution</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>167</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>1671</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -690,7 +775,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -731,16 +816,36 @@
           <t>Toronto FC</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>herdman john</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>167</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>1671</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -754,7 +859,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -795,16 +900,36 @@
           <t>Chicago Fire</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>klopas frank</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>167</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>1671</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -818,7 +943,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>22.06.2024 23:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -859,16 +984,36 @@
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>smith dean</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>167</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>1671</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -882,7 +1027,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
+          <t>23.06.2024 00:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -923,16 +1068,20 @@
           <t>Austin FC</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>167</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>1671</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -946,7 +1095,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
+          <t>23.06.2024 00:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -987,16 +1136,20 @@
           <t>New York City</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>167</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>1671</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -1010,7 +1163,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
+          <t>23.06.2024 00:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1051,336 +1204,20 @@
           <t>Atlanta Utd</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>167</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>1671</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>22.06.2024 22:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mendoza R.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Dick's Sporting Goods Park
- (Commerce City, CO)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>18 061</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>CF Montreal</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>167</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>22.06.2024 22:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Marrufo J.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>America First Field
- (Sandy, UT)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20 213</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Los Angeles Galaxy</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>167</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>22.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Boiko S.
- (Ukr)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BMO Stadium
- (Los Angeles, CA)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>167</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>22.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Unkel T.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Providence Park
- (Portland, OR)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>25 218</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>167</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Badawi M.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Lumen Field
- (Seattle, WA)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>72 000</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>167</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,20 +476,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -544,16 +564,36 @@
           <t>San Jose Earthquakes</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>cherundolo steve</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>gonzalez luchi</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>167</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>1671</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -608,16 +648,36 @@
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>neville phil</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>sartini vanni</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>167</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>1671</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -672,16 +732,36 @@
           <t>FC Dallas</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>schmetzer brian</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>luccin peter</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>167</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>1671</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,40 +476,20 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -518,250 +498,2417 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.06.2024 02:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Boiko S.
- (Ukr)</t>
-        </is>
-      </c>
+          <t>28.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Yankee Stadium
+ (New York, NY)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>54 251</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>167</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>71 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>167</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23 112</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>167</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>68 756</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>167</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>167</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>167</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>22 039</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>167</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Geodis Park
+ (Nashville, TN)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>167</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>167</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>BMO Stadium
  (Los Angeles, CA)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>22 000</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>cherundolo steve</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Onn3tCA5</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>gonzalez luchi</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>167</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>23.06.2024 02:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unkel T.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>167</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Providence Park
  (Portland, OR)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>25 218</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>EqKWmJfM</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>neville phil</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>sartini vanni</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>167</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>23.06.2024 02:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Badawi M.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>167</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PayPal Park
+ (San Jose, CA)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>167</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Lumen Field
  (Seattle, WA)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>72 000</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>167</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BC Place
+ (Vancouver, BC)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>54 405</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>167</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>03.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20 371</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>167</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bank of America Stadium
+ (Charlotte, NC)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>74 500</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>167</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Audi Field
+ (Washington, DC)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>167</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yankee Stadium
+ (New York, NY)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>54 251</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>167</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BMO Field
+ (Toronto, ON)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>30 991</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>167</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>03.07.2024 23:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>68 756</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>167</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>04.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Soldier Field
+ (Chicago, IL)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>61 500</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>167</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>04.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>19 400</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>167</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>04.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>22 423</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>167</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>04.07.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>167</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>05.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>FC Dallas</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>schmetzer brian</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>luccin peter</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>167</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>167</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>05.07.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>167</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>05.07.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>167</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>06.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>23 112</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>167</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>06.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20 371</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>167</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>06.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TQL Stadium
+ (Cincinnati, OH)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>167</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>06.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Inter&amp;Co Stadium
+ (Orlando, FL)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>25 500</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>167</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>06.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Subaru Park
+ (Chester, PA)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>167</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>07.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q2 Stadium
+ (Austin, TX)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20 700</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>167</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07.07.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>167</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07.07.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lumen Field
+ (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>72 000</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>167</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>08.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>22 039</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>167</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>08.07.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>167</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>08.07.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>167</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>08.07.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>167</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>08.07.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Providence Park
+ (Portland, OR)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>25 218</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>167</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>08.07.2024 20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PayPal Park
+ (San Jose, CA)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>167</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>2024</t>
         </is>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,54 +494,59 @@
           <t>season</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>De Oliveira M.
- (Usa)</t>
-        </is>
-      </c>
+          <t>28.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lower.com Field
- (Columbus, OH)</t>
+          <t>Yankee Stadium
+ (New York, NY)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20 371</t>
+          <t>54 251</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sporting Kansas City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -556,56 +561,61 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ford T.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Audi Field
- (Washington, DC)</t>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20 000</t>
+          <t>71 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -620,51 +630,61 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
+          <t>29.06.2024 20:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TQL Stadium
- (Cincinnati, OH)</t>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>23 112</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -679,56 +699,61 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dickerson J.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Red Bull Arena
- (Harrison, NJ)</t>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25 000</t>
+          <t>68 756</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -743,56 +768,61 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Simon N.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Inter&amp;Co Stadium
- (Orlando, FL)</t>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25 500</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York Red Bulls</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -807,56 +837,61 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22.06.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Da Silva A.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Subaru Park
- (Chester, PA)</t>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18 500</t>
+          <t>20 500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -871,56 +906,61 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Fischer D.
- (Can)</t>
-        </is>
-      </c>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Allianz Field
- (Saint Paul, MN)</t>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19 400</t>
+          <t>22 039</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -935,26 +975,31 @@
       <c r="N8" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Rivas V.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Geodis Park
@@ -979,12 +1024,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -999,56 +1044,61 @@
       <c r="N9" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.06.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dujic F.
- (Can)</t>
-        </is>
-      </c>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CITYPARK
- (St. Louis, MO)</t>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22 423</t>
+          <t>18 500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1063,56 +1113,61 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22.06.2024 22:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mendoza R.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dick's Sporting Goods Park
- (Commerce City, CO)</t>
+          <t>BMO Stadium
+ (Los Angeles, CA)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18 061</t>
+          <t>22 000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>jmBZNRn8</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>CF Montreal</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1127,56 +1182,61 @@
       <c r="N11" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22.06.2024 22:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Marrufo J.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>America First Field
- (Sandy, UT)</t>
+          <t>Providence Park
+ (Portland, OR)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20 213</t>
+          <t>25 218</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Los Angeles Galaxy</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1191,56 +1251,61 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Boiko S.
- (Ukr)</t>
-        </is>
-      </c>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BMO Stadium
- (Los Angeles, CA)</t>
+          <t>PayPal Park
+ (San Jose, CA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22 000</t>
+          <t>18 000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Jose Earthquakes</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>Los Angeles Galaxy</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1255,56 +1320,61 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Unkel T.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Providence Park
- (Portland, OR)</t>
+          <t>Lumen Field
+ (Seattle, WA)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25 218</t>
+          <t>72 000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1319,56 +1389,61 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22.06.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Badawi M.
- (Usa)</t>
-        </is>
-      </c>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lumen Field
- (Seattle, WA)</t>
+          <t>BC Place
+ (Vancouver, BC)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72 000</t>
+          <t>54 405</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1383,6 +1458,16 @@
       <c r="N15" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>MLS</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,6 +1471,2145 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>03.07.2024 19:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20 371</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>167</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bank of America Stadium
+ (Charlotte, NC)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>74 500</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>167</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Audi Field
+ (Washington, DC)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>167</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yankee Stadium
+ (New York, NY)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>54 251</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>167</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>03.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BMO Field
+ (Toronto, ON)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>30 991</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>167</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>03.07.2024 20:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>68 756</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>167</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>03.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Soldier Field
+ (Chicago, IL)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>61 500</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>167</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>03.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>19 400</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>167</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>03.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>22 423</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>167</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>03.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>167</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>04.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>167</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>04.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>167</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>04.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>167</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>06.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>23 112</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>167</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>06.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20 371</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>167</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>06.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TQL Stadium
+ (Cincinnati, OH)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>167</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>06.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Inter&amp;Co Stadium
+ (Orlando, FL)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>25 500</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>167</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>06.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Subaru Park
+ (Chester, PA)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>167</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>06.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q2 Stadium
+ (Austin, TX)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20 700</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>167</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>06.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>167</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>06.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lumen Field
+ (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>72 000</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>167</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>07.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>22 039</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>167</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>07.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PayPal Park
+ (San Jose, CA)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>167</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>07.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>167</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>07.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>167</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>07.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>167</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>07.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Providence Park
+ (Portland, OR)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>25 218</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>167</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>09.07.2024 20:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>71 000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>167</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1672</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>US Open Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10.07.2024 00:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Heart Health Park
+ (Sacramento, CA)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>11 569</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>167</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1672</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>US Open Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10.07.2024 22:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>167</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1672</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>US Open Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11.07.2024 00:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BMO Stadium
+ (Los Angeles, CA)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>167</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>US Open Cup</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -516,7 +516,12 @@
           <t>28.06.2024 20:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Boiko S.
+ (Ukr)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Yankee Stadium
@@ -585,7 +590,12 @@
           <t>29.06.2024 20:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>De Oliveira M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Mercedes-Benz Stadium
@@ -654,7 +664,12 @@
           <t>29.06.2024 20:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Freemon J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Saputo Stadium
@@ -723,7 +738,12 @@
           <t>29.06.2024 20:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fierro R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Gillette Stadium
@@ -792,7 +812,12 @@
           <t>29.06.2024 20:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Badawi M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -861,7 +886,12 @@
           <t>29.06.2024 21:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rivas V.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Toyota Stadium
@@ -930,7 +960,12 @@
           <t>29.06.2024 21:30</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lauziere P.
+ (Can)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Shell Energy Stadium
@@ -999,7 +1034,12 @@
           <t>29.06.2024 21:30</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Szpala L.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Geodis Park
@@ -1068,7 +1108,12 @@
           <t>29.06.2024 21:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dujic F.
+ (Can)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Children's Mercy Park
@@ -1137,7 +1182,12 @@
           <t>29.06.2024 23:30</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Penso C.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>BMO Stadium
@@ -1206,7 +1256,12 @@
           <t>29.06.2024 23:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ford T.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Providence Park
@@ -1275,7 +1330,12 @@
           <t>29.06.2024 23:30</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gonzales G.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>PayPal Park
@@ -1344,7 +1404,12 @@
           <t>29.06.2024 23:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dickerson J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Lumen Field
@@ -1413,7 +1478,12 @@
           <t>29.06.2024 23:30</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Allatin M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>BC Place

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -508,50 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.07.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unkel T.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saputo Stadium
- (Montreal, QC)</t>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23 112</t>
+          <t>71 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.07.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dujic F.
- (Can)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Audi Field
- (Washington, DC)</t>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20 000</t>
+          <t>23 112</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.07.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Gonzales G.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TQL Stadium
- (Cincinnati, OH)</t>
+          <t>Chase Stadium
+ (Fort Lauderdale, FL)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>21 550</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,20 +715,15 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.07.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Boiko S.
- (Ukr)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Gillette Stadium
@@ -768,12 +748,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.07.2024 20:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chapman A.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BMO Field
- (Toronto, ON)</t>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30 991</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>New York Red Bulls</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +853,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13.07.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Marrufo J.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q2 Stadium
- (Austin, TX)</t>
+          <t>Inter&amp;Co Stadium
+ (Orlando, FL)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 700</t>
+          <t>25 500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -952,50 +922,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13.07.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Mendoza R.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Soldier Field
- (Chicago, IL)</t>
+          <t>Subaru Park
+ (Chester, PA)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>61 500</t>
+          <t>18 500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1026,50 +991,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.07.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Touchan R.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Toyota Stadium
- (Frisco, TX)</t>
+          <t>Q2 Stadium
+ (Austin, TX)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20 500</t>
+          <t>20 738</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Los Angeles Galaxy</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1100,50 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13.07.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Freemon J.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shell Energy Stadium
- (Houston, TX)</t>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22 039</t>
+          <t>19 400</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Jose Earthquakes</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1174,50 +1129,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13.07.2024 21:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Lauziere P.
- (Can)</t>
-        </is>
-      </c>
+          <t>20.07.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CITYPARK
- (St. Louis, MO)</t>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22 423</t>
+          <t>21 650</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>4r4sKQud</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1248,20 +1198,15 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13.07.2024 22:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ford T.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 22:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Dick's Sporting Goods Park
@@ -1286,12 +1231,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1322,50 +1267,45 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13.07.2024 23:25</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dickerson J.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Providence Park
- (Portland, OR)</t>
+          <t>Lumen Field
+ (Seattle, WA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25 218</t>
+          <t>72 000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1396,50 +1336,45 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13.07.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Szpala L.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BMO Stadium
- (Los Angeles, CA)</t>
+          <t>BC Place
+ (Vancouver, BC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22 000</t>
+          <t>54 405</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1470,50 +1405,45 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13.07.2024 23:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Da Silva A.
- (Usa)</t>
-        </is>
-      </c>
+          <t>20.07.2024 23:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PayPal Park
- (San Jose, CA)</t>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18 000</t>
+          <t>27 000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>Los Angeles Galaxy</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sporting Kansas City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="K15" t="n">

--- a/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,30 +476,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -516,7 +536,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mendoza R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Mercedes-Benz Stadium
@@ -549,26 +574,46 @@
           <t>Columbus Crew</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>valentino rob</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>167</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>1671</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -585,7 +630,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Villarreal A.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Saputo Stadium
@@ -618,26 +668,46 @@
           <t>Toronto FC</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>courtois laurent</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>herdman john</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>167</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>1671</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -654,7 +724,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>De Oliveira M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Chase Stadium
@@ -687,26 +762,46 @@
           <t>Chicago Fire</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>martino gerardo</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>klopas frank</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>167</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>1671</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -723,7 +818,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Allatin M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Gillette Stadium
@@ -756,26 +856,46 @@
           <t>FC Dallas</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>luccin peter</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>167</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>1671</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -792,7 +912,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Unkel T.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -825,26 +950,46 @@
           <t>FC Cincinnati</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>167</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>1671</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -861,7 +1006,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dickerson J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Inter&amp;Co Stadium
@@ -894,26 +1044,46 @@
           <t>New York City</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>cushing nicholas</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>167</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>1671</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -930,7 +1100,12 @@
           <t>20.07.2024 20:30</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Penso C.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Subaru Park
@@ -963,26 +1138,46 @@
           <t>Nashville SC</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>callaghan brian</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>167</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>1671</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -999,7 +1194,12 @@
           <t>20.07.2024 21:30</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Freemon J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Q2 Stadium
@@ -1032,26 +1232,30 @@
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>167</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>1671</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1068,7 +1272,12 @@
           <t>20.07.2024 21:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pekmic I.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Allianz Field
@@ -1101,26 +1310,30 @@
           <t>San Jose Earthquakes</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>167</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>1671</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1137,7 +1350,12 @@
           <t>20.07.2024 21:30</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vazquez R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Children's Mercy Park
@@ -1170,26 +1388,30 @@
           <t>St. Louis City</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>167</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>1671</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1206,7 +1428,12 @@
           <t>20.07.2024 22:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Touchan R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Dick's Sporting Goods Park
@@ -1239,26 +1466,30 @@
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>167</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>1671</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1275,7 +1506,12 @@
           <t>20.07.2024 23:30</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chapman A.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Lumen Field
@@ -1308,26 +1544,30 @@
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>167</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>1671</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1344,7 +1584,12 @@
           <t>20.07.2024 23:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bazakos F.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>BC Place
@@ -1377,26 +1622,30 @@
           <t>Houston Dynamo</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>167</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>1671</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1413,7 +1662,12 @@
           <t>20.07.2024 23:45</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Boiko S.
+ (Ukr)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Dignity Health Sports Park
@@ -1446,26 +1700,30 @@
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>167</v>
       </c>
-      <c r="L15" t="n">
+      <c r="P15" t="n">
         <v>1671</v>
       </c>
-      <c r="M15" t="n">
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
